--- a/output/pdf_financials_xlsx/LSD.H.xlsx
+++ b/output/pdf_financials_xlsx/LSD.H.xlsx
@@ -6861,31 +6861,31 @@
         <v>0.402561</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.402561</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.402561</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.402561</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.402561</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.402561</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.402561</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.402561</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.402561</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.40483</v>
       </c>
       <c r="N92" s="1" t="inlineStr">
         <is>
@@ -6893,19 +6893,19 @@
         </is>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.40483</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.40483</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>0.40483</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>0.40483</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>0.40483</v>
       </c>
       <c r="T92" s="1" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>-0.127752</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0.239027</v>
+        <v>0.156752</v>
       </c>
       <c r="G118" s="3" t="n">
         <v>0.02643</v>
@@ -10738,7 +10738,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -12587,7 +12591,11 @@
           <t>Share-based payment reserve 404,830</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -13590,7 +13598,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -16781,7 +16793,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -19346,7 +19362,11 @@
           <t>Share-based payment reserve 402,561</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -28124,7 +28144,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E167" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/LSD.H.xlsx
+++ b/output/pdf_financials_xlsx/LSD.H.xlsx
@@ -1017,28 +1017,28 @@
         <v>0.198023</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.16712</v>
+        <v>0.423521</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.10263</v>
+        <v>0.176766</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.08552</v>
+        <v>0.204176</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.10684</v>
+        <v>0.110949</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.07343</v>
+        <v>0.08089499999999999</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.040556</v>
+        <v>0.046556</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.049237</v>
+        <v>0.061834</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.058966</v>
+        <v>0.07912</v>
       </c>
       <c r="N10" s="1" t="inlineStr">
         <is>
@@ -1046,19 +1046,19 @@
         </is>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.078586</v>
+        <v>0.193066</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.203884</v>
+        <v>0.218634</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.155222</v>
+        <v>0.173653</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.039477</v>
+        <v>0.055977</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.038008</v>
+        <v>0.055008</v>
       </c>
       <c r="T10" s="1" t="inlineStr">
         <is>
@@ -1099,22 +1099,22 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.08552</v>
+        <v>-0.204176</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.10684</v>
+        <v>-0.110949</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.07343</v>
+        <v>-0.08089499999999999</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.040556</v>
+        <v>-0.046556</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.049237</v>
+        <v>-0.061834</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.058966</v>
+        <v>-0.07912</v>
       </c>
       <c r="N11" s="1" t="inlineStr">
         <is>
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-0.078586</v>
+        <v>-0.193066</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.203884</v>
+        <v>-0.218634</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-0.155222</v>
+        <v>-0.173653</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-0.039477</v>
+        <v>-0.055977</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>-0.038008</v>
+        <v>-0.055008</v>
       </c>
       <c r="T11" s="1" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.002846</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -1158,19 +1158,19 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.0009479999999999999</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.005372</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.011776</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.003594</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
@@ -2261,7 +2261,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.100769</v>
+        <v>-1.103615</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-1.975113</v>
@@ -2270,19 +2270,19 @@
         <v>-0.186412</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.233437</v>
+        <v>-0.234385</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.419597</v>
+        <v>-0.424969</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.145753</v>
+        <v>-0.157529</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-0.205624</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.063573</v>
+        <v>-0.067167</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-0.309022</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.100769</v>
+        <v>-1.103615</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-1.975113</v>
@@ -2406,19 +2406,19 @@
         <v>-0.186412</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.233437</v>
+        <v>-0.234385</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.419597</v>
+        <v>-0.424969</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.145753</v>
+        <v>-0.157529</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-0.205624</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.062475</v>
+        <v>-0.066069</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-0.307924</v>
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.125896</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.819685</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.819685</v>
@@ -2762,22 +2762,22 @@
         <v>0.163604</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.055422</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.008394</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.002438</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.003172</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.121557</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.180689</v>
       </c>
       <c r="N34" s="1" t="inlineStr">
         <is>
@@ -2785,13 +2785,13 @@
         </is>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.009745999999999999</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.000799</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.000726</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>0</v>
@@ -2880,10 +2880,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.125896</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.819685</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.819685</v>
@@ -2898,22 +2898,22 @@
         <v>0.163604</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.055422</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.008394</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.002438</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.003172</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.121557</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.180689</v>
       </c>
       <c r="N36" s="1" t="inlineStr">
         <is>
@@ -2921,13 +2921,13 @@
         </is>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.009745999999999999</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.000799</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.000726</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>0</v>
@@ -3699,7 +3699,7 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.2951</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
@@ -3714,13 +3714,13 @@
         <v>0.1</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.057422</v>
+        <v>0.002</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.008394</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.002438</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0</v>
@@ -11253,7 +11253,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -19800,7 +19800,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -21374,7 +21374,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
@@ -33945,7 +33945,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -34246,7 +34246,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -36051,7 +36051,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -39813,7 +39813,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -41133,7 +41133,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -42017,7 +42017,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -44802,7 +44802,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E319" s="5" t="n">

--- a/output/pdf_financials_xlsx/LSD.H.xlsx
+++ b/output/pdf_financials_xlsx/LSD.H.xlsx
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.225144</v>
+        <v>0.285144</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0.146007</v>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.257469</v>
+        <v>0.317469</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>1.897613</v>
@@ -6580,7 +6580,7 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>0</v>
+        <v>19.339282</v>
       </c>
       <c r="C88" s="3" t="n">
         <v>19.482372</v>
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.385651</v>
       </c>
       <c r="C92" s="3" t="n">
         <v>0.402561</v>
@@ -21600,7 +21600,11 @@
           <t>Mineral properties – Note 3</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>MineralProperties</t>
+        </is>
+      </c>
       <c r="E107" s="5" t="n">
         <v>1.460165</v>
       </c>
@@ -22151,7 +22155,11 @@
           <t>Share capital – Note 5</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E112" s="5" t="n">
         <v>19.339282</v>
       </c>
@@ -22260,7 +22268,11 @@
           <t>Contributed surplus – Note 5</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E113" s="5" t="n">
         <v>0.385651</v>
       </c>
@@ -44023,7 +44035,11 @@
           <t>Management fees – Note 6</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E312" s="5" t="n">
         <v>0.06</v>
       </c>

--- a/output/pdf_financials_xlsx/LSD.H.xlsx
+++ b/output/pdf_financials_xlsx/LSD.H.xlsx
@@ -1495,7 +1495,7 @@
         <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.04</v>
+        <v>-0.0285</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -2573,7 +2573,7 @@
         <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-21.45784606141235</v>
+        <v>-15.2887153187563</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
@@ -4869,51 +4869,49 @@
         <v>0</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.091088</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.131867</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.083437</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.026413</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.02311</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.095517</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.110898</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.14132</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.073754</v>
+      </c>
+      <c r="N64" s="3" t="n">
+        <v>0.033509</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>0.103855</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>0.28472</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>0.429477</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>0</v>
+        <v>0.45581</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>0</v>
+        <v>0.481526</v>
       </c>
       <c r="T64" s="1" t="inlineStr">
         <is>
@@ -24350,7 +24348,11 @@
           <t>Proceeds from shares issued</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -30249,7 +30251,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -43258,7 +43264,11 @@
           <t>Future income tax recovery (Note 14)</t>
         </is>
       </c>
-      <c r="D305" t="inlineStr"/>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr">
         <is>
           <t>-</t>
